--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-09).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-09).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-180</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>R$ 689.689,02</t>
-  </si>
-  <si>
-    <t>R$ 3.629,94
-R$ 3.707,93</t>
-  </si>
-  <si>
-    <t>(10.1%)
-(8.1%)</t>
+185</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>R$ 707.554,13</t>
+  </si>
+  <si>
+    <t>R$ 3.628,48
+R$ 3.704,28</t>
+  </si>
+  <si>
+    <t>(9.8%)
+(7.9%)</t>
   </si>
   <si>
     <t>41.0</t>
   </si>
   <si>
-    <t>(14.0%)</t>
-  </si>
-  <si>
-    <t>3.0%</t>
-  </si>
-  <si>
-    <t>(40.2%)</t>
+    <t>(13.6%)</t>
+  </si>
+  <si>
+    <t>7.7%</t>
+  </si>
+  <si>
+    <t>(35.3%)</t>
   </si>
   <si>
     <t>4.4%</t>
@@ -950,10 +950,10 @@
     <t>25.8</t>
   </si>
   <si>
-    <t>75.1%</t>
-  </si>
-  <si>
-    <t>7.5%</t>
+    <t>75.4%</t>
+  </si>
+  <si>
+    <t>7.4%</t>
   </si>
   <si>
     <t>4.5</t>
@@ -962,7 +962,7 @@
     <t>6.4</t>
   </si>
   <si>
-    <t>11.2</t>
+    <t>11.1</t>
   </si>
   <si>
     <t>17.7</t>
@@ -971,10 +971,10 @@
     <t>77.1%</t>
   </si>
   <si>
-    <t>-R$ 28.854,32</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>-R$ 29.037,52</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>6765.5600000000004</v>
+      </c>
+      <c r="P6" s="5">
+        <v>6765.5600000000004</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.11957716086156456</v>
+      </c>
+      <c r="R6" s="7">
+        <v>79</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.19696969696969702</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.30970209413559263</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.0035860889564204588</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.033935431804610408</v>
+      </c>
+      <c r="W6" s="6">
+        <v>-0.0038234528996860567</v>
+      </c>
+      <c r="X6" s="8">
+        <v>20.168306557377047</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.96721311475409832</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>4.8557013157894735</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.5412573770491802</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>7.5128399999999997</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>14.471857377049181</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.95081967213114749</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -4388,7 +4424,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4424,25 +4460,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>3507.98</v>
+      </c>
+      <c r="P24" s="5">
+        <v>3507.98</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0.18097899272825213</v>
+      </c>
+      <c r="R24" s="7">
+        <v>42</v>
+      </c>
+      <c r="S24" s="6">
+        <v>0.050000000000000044</v>
+      </c>
+      <c r="T24" s="6">
+        <v>3.8242698076955968</v>
+      </c>
+      <c r="U24" s="6">
+        <v>3.4778909799941844</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.025887975416051402</v>
+      </c>
+      <c r="W24" s="6">
+        <v>-0.0090666138347425002</v>
+      </c>
+      <c r="X24" s="8">
+        <v>29.473334285714287</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.54285714285714282</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>3.1264219512195122</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>10.023808571428571</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>20.127142857142857</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-165.69999999999999</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5924,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5960,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>2942.02</v>
+      </c>
+      <c r="P36" s="5">
+        <v>2942.02</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.27604333833568995</v>
+      </c>
+      <c r="R36" s="7">
+        <v>34</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.17241379310344818</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.32923515135859038</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.014532056206280038</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.16602657357869763</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.10080607881659541</v>
+      </c>
+      <c r="X36" s="8">
+        <v>26.297368421052632</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>4.9515624999999996</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>7</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>12.512280000000001</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>18.267542105263157</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.78947368421052633</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>-17.5</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7845,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7881,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>158.30000000000001</v>
+      </c>
+      <c r="P51" s="5">
+        <v>158.30000000000001</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.83231997966230953</v>
+      </c>
+      <c r="R51" s="7">
+        <v>2</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.75</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.25274794693619707</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.21032217308907136</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.59833228048010101</v>
+      </c>
+      <c r="X51" s="8">
+        <v>23.63335</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>4.2000000000000002</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>7.7333499999999997</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>11.933332999999999</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>18.858350000000002</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12604,7 +12746,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12643,7 +12785,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12677,25 +12819,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>4491.25</v>
+      </c>
+      <c r="P89" s="5">
+        <v>4491.25</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.1873805836204151</v>
+      </c>
+      <c r="R89" s="7">
+        <v>41</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.18000000000000005</v>
+      </c>
+      <c r="T89" s="6">
+        <v>3.8180770832173669</v>
+      </c>
+      <c r="U89" s="6">
+        <v>3.487632329529641</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.032994823267464508</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.009486891177289172</v>
+      </c>
+      <c r="X89" s="8">
+        <v>29.919999999999998</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>4.9987804878048774</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>6.4091649999999998</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>19.690000000000001</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -15441,7 +15617,9 @@
       <c r="AB111" s="8">
         <v>3.9197937500000002</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>8.2239570000000004</v>
+      </c>
       <c r="AD111" s="8">
         <v>15.16770625</v>
       </c>
@@ -15453,7 +15631,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15806,7 +15984,7 @@
         <v>-126.90000000000001</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -16681,7 +16859,7 @@
         <v>-65.099999999999994</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -16943,7 +17121,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17336,7 +17514,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18513,7 +18691,7 @@
         <v>0</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18644,7 +18822,7 @@
         <v>-374.69999999999999</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20829,7 +21007,7 @@
         <v>-1541.0999999999999</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -20956,7 +21134,7 @@
         <v>-149.81999999999999</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -22113,7 +22291,7 @@
         <v>-469.43000000000001</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24191,7 +24369,9 @@
       <c r="AB179" s="8">
         <v>1.6651499999999999</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>3.789393</v>
+      </c>
       <c r="AD179" s="8">
         <v>10.739395454545454</v>
       </c>
@@ -28276,7 +28456,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
